--- a/backend/data/glossary_master.xlsx
+++ b/backend/data/glossary_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H667"/>
+  <dimension ref="A1:H668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10189,13 +10189,13 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>有冇搞錯</t>
+          <t>有冇</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>expresses disbelief, similar to "Seriously?"</t>
+          <t>have or have not</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -16543,23 +16543,23 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>m巾</t>
+          <t>mud</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>姨媽巾</t>
+          <t>乜</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>卫生巾</t>
+          <t>什么</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>sanitary napkin</t>
+          <t>what</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -16581,23 +16581,23 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>shiba</t>
+          <t>m巾</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>西八</t>
+          <t>姨媽巾</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>西八</t>
+          <t>卫生巾</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>damn it</t>
+          <t>sanitary napkin</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -16619,23 +16619,23 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>sls</t>
+          <t>shiba</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
-          <t>笑撚死</t>
+          <t>西八</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>笑死</t>
+          <t>西八</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>lol</t>
+          <t>damn it</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -16657,23 +16657,23 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>射波</t>
+          <t>sls</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
-          <t>射波</t>
+          <t>笑撚死</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>翘课，请假</t>
+          <t>笑死</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>take leave on purpose / skip work or class for personal reasons</t>
+          <t>lol</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -16690,28 +16690,28 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>动词</t>
+          <t>俚语</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>射波</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
-          <t>睇睇</t>
+          <t>射波</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>看一看</t>
+          <t>翘课，请假</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>take a look</t>
+          <t>take leave on purpose / skip work or class for personal reasons</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -16733,19 +16733,23 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>chur</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
-          <t>消耗能量、資源</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr"/>
+          <t>睇睇</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>看一看</t>
+        </is>
+      </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>to exhaust; to exploit</t>
+          <t>take a look</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -16767,23 +16771,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>chut</t>
+          <t>chur</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
-          <t>出</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>出</t>
-        </is>
-      </c>
+          <t>消耗能量、資源</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
-          <t>go out</t>
+          <t>to exhaust; to exploit</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -16805,23 +16805,23 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>chut</t>
         </is>
       </c>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
-          <t>返</t>
+          <t>出</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>回</t>
+          <t>出</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>return</t>
+          <t>go out</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -16843,23 +16843,23 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>jap</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
-          <t>食</t>
+          <t>返</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>吃</t>
+          <t>回</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>eat</t>
+          <t>return</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -16881,23 +16881,23 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>yurk</t>
+          <t>jap</t>
         </is>
       </c>
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
-          <t>約</t>
+          <t>食</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>约</t>
+          <t>吃</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>date/go out</t>
+          <t>eat</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -16919,23 +16919,23 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>yurk</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
-          <t>摺</t>
+          <t>約</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>折叠</t>
+          <t>约</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>fold</t>
+          <t>date/go out</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -16952,28 +16952,28 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>基本词</t>
+          <t>动词</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>dik</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>的</t>
+          <t>摺</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>的</t>
+          <t>折叠</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>(possessive particle)</t>
+          <t>fold</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -16995,23 +16995,23 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>mah</t>
+          <t>dik</t>
         </is>
       </c>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>嗎</t>
+          <t>的</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>吗</t>
+          <t>的</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>(question particle)</t>
+          <t>(possessive particle)</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -17028,28 +17028,28 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>常用句</t>
+          <t>基本词</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>nvm</t>
+          <t>mah</t>
         </is>
       </c>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
         <is>
-          <t>無所謂</t>
+          <t>嗎</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>无所谓</t>
+          <t>吗</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>never mind</t>
+          <t>(question particle)</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -17066,28 +17066,28 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>形容词</t>
+          <t>常用句</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>nvm</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>似</t>
+          <t>無所謂</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>像</t>
+          <t>无所谓</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>similar</t>
+          <t>never mind</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -17109,23 +17109,23 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>minghin</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>明顯</t>
+          <t>似</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>明显</t>
+          <t>像</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>obvious</t>
+          <t>similar</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -17142,28 +17142,28 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>日常</t>
+          <t>形容词</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>daiga</t>
+          <t>minghin</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>大家</t>
+          <t>明顯</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>大家</t>
+          <t>明显</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>obvious</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -17185,23 +17185,23 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>jaijai</t>
+          <t>daiga</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>仔仔</t>
+          <t>大家</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>男生</t>
+          <t>大家</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>boy</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -17218,28 +17218,28 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>疑问词</t>
+          <t>日常</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>dim</t>
+          <t>jaijai</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>點</t>
+          <t>仔仔</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>怎麼樣</t>
+          <t>男生</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>how</t>
+          <t>boy</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -17256,28 +17256,28 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>补充</t>
+          <t>疑问词</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>dim</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>打</t>
+          <t>點</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>打</t>
+          <t>怎麼樣</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>hit/do</t>
+          <t>how</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -17299,23 +17299,23 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>da</t>
         </is>
       </c>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>梗</t>
+          <t>打</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>一定</t>
+          <t>打</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>surely</t>
+          <t>hit/do</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -17337,23 +17337,23 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>guo</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>過</t>
+          <t>梗</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>过</t>
+          <t>一定</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>(experience)</t>
+          <t>surely</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -17375,23 +17375,23 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>horneng</t>
+          <t>guo</t>
         </is>
       </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>可能</t>
+          <t>過</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>可能</t>
+          <t>过</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>(experience)</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -17413,23 +17413,23 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>horyi</t>
+          <t>horneng</t>
         </is>
       </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>可以</t>
+          <t>可能</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>可以</t>
+          <t>可能</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>can</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -17451,23 +17451,23 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>jor</t>
+          <t>horyi</t>
         </is>
       </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
-          <t>咗</t>
+          <t>可以</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>了</t>
+          <t>可以</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>(past tense)</t>
+          <t>can</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -17489,23 +17489,23 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>ju</t>
+          <t>jor</t>
         </is>
       </c>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>住</t>
+          <t>咗</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>着</t>
+          <t>了</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>(continuous)</t>
+          <t>(past tense)</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -17527,23 +17527,23 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>ju</t>
         </is>
       </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>嚟</t>
+          <t>住</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>来</t>
+          <t>着</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>come</t>
+          <t>(continuous)</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -17565,23 +17565,23 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>liu</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr">
         <is>
-          <t>了</t>
+          <t>嚟</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>了</t>
+          <t>来</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>(completed)</t>
+          <t>come</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -17603,23 +17603,23 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>mei</t>
+          <t>liu</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>了</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>还没</t>
+          <t>了</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>not yet</t>
+          <t>(completed)</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -17641,23 +17641,23 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>mei</t>
         </is>
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>屏幕</t>
+          <t>未</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>屏幕</t>
+          <t>还没</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>not yet</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -17674,28 +17674,28 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>语气词</t>
+          <t>补充</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>gua</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
-          <t>掛</t>
+          <t>屏幕</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>吧</t>
+          <t>屏幕</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>huh</t>
+          <t>screen</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -17723,11 +17723,19 @@
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>啩</t>
-        </is>
-      </c>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
+          <t>掛</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>吧</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>huh</t>
+        </is>
+      </c>
       <c r="H489" t="inlineStr">
         <is>
           <t>False</t>
@@ -17747,25 +17755,17 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>har</t>
+          <t>gua</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>吓</t>
-        </is>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>啊？</t>
-        </is>
-      </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>huh</t>
-        </is>
-      </c>
+          <t>啩</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr">
         <is>
           <t>False</t>
@@ -17778,24 +17778,32 @@
           <t>token</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr"/>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>语气词</t>
+        </is>
+      </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>7tau</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>7tou</t>
-        </is>
-      </c>
+          <t>har</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>柒頭</t>
-        </is>
-      </c>
-      <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr"/>
+          <t>吓</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>啊？</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>huh</t>
+        </is>
+      </c>
       <c r="H491" t="inlineStr">
         <is>
           <t>False</t>
@@ -17811,28 +17819,24 @@
       <c r="B492" t="inlineStr"/>
       <c r="C492" t="inlineStr">
         <is>
-          <t>aa</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr"/>
+          <t>7tau</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>7tou</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>A錢</t>
-        </is>
-      </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>go dutch</t>
-        </is>
-      </c>
+          <t>柒頭</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -17845,24 +17849,28 @@
       <c r="B493" t="inlineStr"/>
       <c r="C493" t="inlineStr">
         <is>
-          <t>b4</t>
+          <t>aa</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>之前</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>之前</t>
-        </is>
-      </c>
-      <c r="G493" t="inlineStr"/>
+          <t>A錢</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>go dutch</t>
+        </is>
+      </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -17875,18 +17883,18 @@
       <c r="B494" t="inlineStr"/>
       <c r="C494" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>b4</t>
         </is>
       </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>師奶</t>
+          <t>之前</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>阿婆</t>
+          <t>之前</t>
         </is>
       </c>
       <c r="G494" t="inlineStr"/>
@@ -17905,16 +17913,20 @@
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr">
         <is>
-          <t>chau</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>臭</t>
-        </is>
-      </c>
-      <c r="F495" t="inlineStr"/>
+          <t>師奶</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>阿婆</t>
+        </is>
+      </c>
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr">
         <is>
@@ -17931,13 +17943,13 @@
       <c r="B496" t="inlineStr"/>
       <c r="C496" t="inlineStr">
         <is>
-          <t>cheng</t>
+          <t>chau</t>
         </is>
       </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>請</t>
+          <t>臭</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -17957,20 +17969,16 @@
       <c r="B497" t="inlineStr"/>
       <c r="C497" t="inlineStr">
         <is>
-          <t>chill</t>
+          <t>cheng</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>放鬆/舒服</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>放松/舒服</t>
-        </is>
-      </c>
+          <t>請</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
       <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr">
         <is>
@@ -17987,18 +17995,18 @@
       <c r="B498" t="inlineStr"/>
       <c r="C498" t="inlineStr">
         <is>
-          <t>chur到爆</t>
+          <t>chill</t>
         </is>
       </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>超級忙</t>
+          <t>放鬆/舒服</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>超级忙</t>
+          <t>放松/舒服</t>
         </is>
       </c>
       <c r="G498" t="inlineStr"/>
@@ -18017,25 +18025,21 @@
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr">
         <is>
-          <t>cuz</t>
+          <t>chur到爆</t>
         </is>
       </c>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>因為</t>
+          <t>超級忙</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>因为</t>
-        </is>
-      </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>because</t>
-        </is>
-      </c>
+          <t>超级忙</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr">
         <is>
           <t>False</t>
@@ -18051,17 +18055,25 @@
       <c r="B500" t="inlineStr"/>
       <c r="C500" t="inlineStr">
         <is>
-          <t>din</t>
+          <t>cuz</t>
         </is>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>癲</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
+          <t>因為</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>because</t>
+        </is>
+      </c>
       <c r="H500" t="inlineStr">
         <is>
           <t>False</t>
@@ -18077,20 +18089,16 @@
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>ding</t>
+          <t>din</t>
         </is>
       </c>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>定係</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>還是</t>
-        </is>
-      </c>
+          <t>癲</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr">
         <is>
@@ -18113,19 +18121,15 @@
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>頂</t>
+          <t>定係</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>靠</t>
-        </is>
-      </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>damn / f*ck (mild profanity/exclamation of frustration)</t>
-        </is>
-      </c>
+          <t>還是</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr">
         <is>
           <t>False</t>
@@ -18141,21 +18145,25 @@
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
-          <t>dou</t>
+          <t>ding</t>
         </is>
       </c>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>到/都</t>
+          <t>頂</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>都</t>
-        </is>
-      </c>
-      <c r="G503" t="inlineStr"/>
+          <t>靠</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>damn / f*ck (mild profanity/exclamation of frustration)</t>
+        </is>
+      </c>
       <c r="H503" t="inlineStr">
         <is>
           <t>False</t>
@@ -18171,25 +18179,21 @@
       <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr">
         <is>
-          <t>dukham</t>
+          <t>dou</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>得閒</t>
+          <t>到/都</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>有空</t>
-        </is>
-      </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>free / have time</t>
-        </is>
-      </c>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>False</t>
@@ -18205,23 +18209,23 @@
       <c r="B505" t="inlineStr"/>
       <c r="C505" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>dukham</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>瞓</t>
+          <t>得閒</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>睡觉</t>
+          <t>有空</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>free / have time</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -18239,21 +18243,25 @@
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>flop</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>失敗/表現差</t>
+          <t>瞓</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>搞砸/失败/表现差</t>
-        </is>
-      </c>
-      <c r="G506" t="inlineStr"/>
+          <t>睡觉</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
       <c r="H506" t="inlineStr">
         <is>
           <t>False</t>
@@ -18269,16 +18277,20 @@
       <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>gao</t>
+          <t>flop</t>
         </is>
       </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
-          <t>搞</t>
-        </is>
-      </c>
-      <c r="F507" t="inlineStr"/>
+          <t>失敗/表現差</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>搞砸/失败/表现差</t>
+        </is>
+      </c>
       <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr">
         <is>
@@ -18295,20 +18307,16 @@
       <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
-          <t>gei</t>
+          <t>gao</t>
         </is>
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>幾</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>几</t>
-        </is>
-      </c>
+          <t>搞</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr">
         <is>
@@ -18325,18 +18333,18 @@
       <c r="B509" t="inlineStr"/>
       <c r="C509" t="inlineStr">
         <is>
-          <t>har</t>
+          <t>gei</t>
         </is>
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>吓？</t>
+          <t>幾</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>啥</t>
+          <t>几</t>
         </is>
       </c>
       <c r="G509" t="inlineStr"/>
@@ -18355,18 +18363,18 @@
       <c r="B510" t="inlineStr"/>
       <c r="C510" t="inlineStr">
         <is>
-          <t>icic</t>
+          <t>har</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>我明白了</t>
+          <t>吓？</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>我明白了</t>
+          <t>啥</t>
         </is>
       </c>
       <c r="G510" t="inlineStr"/>
@@ -18385,24 +18393,24 @@
       <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr">
         <is>
-          <t>jap</t>
+          <t>icic</t>
         </is>
       </c>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>jap</t>
+          <t>我明白了</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>吃</t>
+          <t>我明白了</t>
         </is>
       </c>
       <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -18415,24 +18423,24 @@
       <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr">
         <is>
-          <t>jhgg</t>
+          <t>jap</t>
         </is>
       </c>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
-          <t>即係咁講</t>
+          <t>jap</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>意思就是</t>
+          <t>吃</t>
         </is>
       </c>
       <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -18445,18 +18453,18 @@
       <c r="B513" t="inlineStr"/>
       <c r="C513" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>jhgg</t>
         </is>
       </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
-          <t>其實</t>
+          <t>即係咁講</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>其实</t>
+          <t>意思就是</t>
         </is>
       </c>
       <c r="G513" t="inlineStr"/>
@@ -18475,16 +18483,20 @@
       <c r="B514" t="inlineStr"/>
       <c r="C514" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
-          <t>躝</t>
-        </is>
-      </c>
-      <c r="F514" t="inlineStr"/>
+          <t>其實</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>其实</t>
+        </is>
+      </c>
       <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr">
         <is>
@@ -18501,20 +18513,16 @@
       <c r="B515" t="inlineStr"/>
       <c r="C515" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
-          <t>來</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>来</t>
-        </is>
-      </c>
+          <t>躝</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr">
         <is>
@@ -18531,16 +18539,20 @@
       <c r="B516" t="inlineStr"/>
       <c r="C516" t="inlineStr">
         <is>
-          <t>lun</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr">
         <is>
-          <t>撚（髒話）</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr"/>
+          <t>來</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>来</t>
+        </is>
+      </c>
       <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr">
         <is>
@@ -18557,25 +18569,17 @@
       <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>lun</t>
         </is>
       </c>
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr">
         <is>
-          <t>乜</t>
-        </is>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>什么</t>
-        </is>
-      </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
+          <t>撚（髒話）</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
           <t>False</t>
@@ -18591,23 +18595,23 @@
       <c r="B518" t="inlineStr"/>
       <c r="C518" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>mat</t>
         </is>
       </c>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
-          <t>咪</t>
+          <t>乜</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>麦克风</t>
+          <t>什么</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>microphone</t>
+          <t>what</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -18625,19 +18629,23 @@
       <c r="B519" t="inlineStr"/>
       <c r="C519" t="inlineStr">
         <is>
-          <t>mnyy</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
-          <t>must need 要有</t>
-        </is>
-      </c>
-      <c r="F519" t="inlineStr"/>
+          <t>咪</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>麦克风</t>
+        </is>
+      </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>must need</t>
+          <t>microphone</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -18655,23 +18663,19 @@
       <c r="B520" t="inlineStr"/>
       <c r="C520" t="inlineStr">
         <is>
-          <t>ofc</t>
+          <t>mnyy</t>
         </is>
       </c>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
-          <t>當然</t>
-        </is>
-      </c>
-      <c r="F520" t="inlineStr">
-        <is>
-          <t>當然</t>
-        </is>
-      </c>
+          <t>must need 要有</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
-          <t>of course</t>
+          <t>must need</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -18689,23 +18693,23 @@
       <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
-          <t>ootd</t>
+          <t>ofc</t>
         </is>
       </c>
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>今日穿搭</t>
+          <t>當然</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>今日穿搭</t>
+          <t>當然</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>outfit of the day</t>
+          <t>of course</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -18723,21 +18727,25 @@
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr">
         <is>
-          <t>piu</t>
+          <t>ootd</t>
         </is>
       </c>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
-          <t>漂</t>
+          <t>今日穿搭</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>漂染</t>
-        </is>
-      </c>
-      <c r="G522" t="inlineStr"/>
+          <t>今日穿搭</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>outfit of the day</t>
+        </is>
+      </c>
       <c r="H522" t="inlineStr">
         <is>
           <t>False</t>
@@ -18753,25 +18761,21 @@
       <c r="B523" t="inlineStr"/>
       <c r="C523" t="inlineStr">
         <is>
-          <t>pua</t>
+          <t>piu</t>
         </is>
       </c>
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
-          <t>情緒操控</t>
+          <t>漂</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>情绪操控</t>
-        </is>
-      </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>emotional manipulation</t>
-        </is>
-      </c>
+          <t>漂染</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr">
         <is>
           <t>False</t>
@@ -18787,21 +18791,25 @@
       <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>shiba</t>
+          <t>pua</t>
         </is>
       </c>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
-          <t>西巴（韩语骂人的词语）</t>
+          <t>情緒操控</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>西巴（韩语骂人的词语）</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr"/>
+          <t>情绪操控</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>emotional manipulation</t>
+        </is>
+      </c>
       <c r="H524" t="inlineStr">
         <is>
           <t>False</t>
@@ -18817,18 +18825,18 @@
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>shrg</t>
+          <t>shiba</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
-          <t>想</t>
+          <t>西巴（韩语骂人的词语）</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>想</t>
+          <t>西巴（韩语骂人的词语）</t>
         </is>
       </c>
       <c r="G525" t="inlineStr"/>
@@ -18847,18 +18855,18 @@
       <c r="B526" t="inlineStr"/>
       <c r="C526" t="inlineStr">
         <is>
-          <t>tai</t>
+          <t>shrg</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
-          <t>太</t>
+          <t>想</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>太</t>
+          <t>想</t>
         </is>
       </c>
       <c r="G526" t="inlineStr"/>
@@ -18877,25 +18885,21 @@
       <c r="B527" t="inlineStr"/>
       <c r="C527" t="inlineStr">
         <is>
-          <t>teng</t>
+          <t>tai</t>
         </is>
       </c>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t>聽</t>
+          <t>太</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>听</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>listen</t>
-        </is>
-      </c>
+          <t>太</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr">
         <is>
           <t>False</t>
@@ -18911,23 +18915,23 @@
       <c r="B528" t="inlineStr"/>
       <c r="C528" t="inlineStr">
         <is>
-          <t>tim</t>
+          <t>teng</t>
         </is>
       </c>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
-          <t>添</t>
+          <t>聽</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>还</t>
+          <t>听</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>also</t>
+          <t>listen</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -18945,23 +18949,23 @@
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr">
         <is>
-          <t>yam</t>
+          <t>tim</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
-          <t>飲</t>
+          <t>添</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>喝</t>
+          <t>还</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>drink</t>
+          <t>also</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -18979,23 +18983,23 @@
       <c r="B530" t="inlineStr"/>
       <c r="C530" t="inlineStr">
         <is>
-          <t>yum</t>
+          <t>yam</t>
         </is>
       </c>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
-          <t>好食</t>
+          <t>飲</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>好吃</t>
+          <t>喝</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>yummy</t>
+          <t>drink</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -19013,23 +19017,23 @@
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr">
         <is>
-          <t>zau</t>
+          <t>yum</t>
         </is>
       </c>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
-          <t>走</t>
+          <t>好食</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>走</t>
+          <t>好吃</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>leave</t>
+          <t>yummy</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -19047,23 +19051,23 @@
       <c r="B532" t="inlineStr"/>
       <c r="C532" t="inlineStr">
         <is>
-          <t>ze</t>
+          <t>zau</t>
         </is>
       </c>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>啫</t>
+          <t>走</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>而已</t>
+          <t>走</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>only</t>
+          <t>leave</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -19081,21 +19085,25 @@
       <c r="B533" t="inlineStr"/>
       <c r="C533" t="inlineStr">
         <is>
-          <t>zhongyiu</t>
+          <t>ze</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
-          <t>仲要</t>
+          <t>啫</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>还要</t>
-        </is>
-      </c>
-      <c r="G533" t="inlineStr"/>
+          <t>而已</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>only</t>
+        </is>
+      </c>
       <c r="H533" t="inlineStr">
         <is>
           <t>False</t>
@@ -19111,29 +19119,21 @@
       <c r="B534" t="inlineStr"/>
       <c r="C534" t="inlineStr">
         <is>
-          <t>zihai</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>jac hai</t>
-        </is>
-      </c>
+          <t>zhongyiu</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
-          <t>即係</t>
+          <t>仲要</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>就是</t>
-        </is>
-      </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>so / that means / in other words</t>
-        </is>
-      </c>
+          <t>还要</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
       <c r="H534" t="inlineStr">
         <is>
           <t>False</t>
@@ -19149,23 +19149,27 @@
       <c r="B535" t="inlineStr"/>
       <c r="C535" t="inlineStr">
         <is>
-          <t>zo</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr"/>
+          <t>zihai</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>jac hai</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>做</t>
+          <t>即係</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>做</t>
+          <t>就是</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>so / that means / in other words</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -19183,21 +19187,25 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>入pool</t>
+          <t>zo</t>
         </is>
       </c>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>開始拍拖</t>
+          <t>做</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>开始谈恋爱</t>
-        </is>
-      </c>
-      <c r="G536" t="inlineStr"/>
+          <t>做</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>do</t>
+        </is>
+      </c>
       <c r="H536" t="inlineStr">
         <is>
           <t>False</t>
@@ -19213,18 +19221,18 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>冇mood</t>
+          <t>入pool</t>
         </is>
       </c>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t>冇mood</t>
+          <t>開始拍拖</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>没心情/没情绪</t>
+          <t>开始谈恋爱</t>
         </is>
       </c>
       <c r="G537" t="inlineStr"/>
@@ -19243,18 +19251,18 @@
       <c r="B538" t="inlineStr"/>
       <c r="C538" t="inlineStr">
         <is>
-          <t>冇晒face</t>
+          <t>冇mood</t>
         </is>
       </c>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>冇晒菲士</t>
+          <t>冇mood</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>没面子</t>
+          <t>没心情/没情绪</t>
         </is>
       </c>
       <c r="G538" t="inlineStr"/>
@@ -19273,18 +19281,18 @@
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>出pool</t>
+          <t>冇晒face</t>
         </is>
       </c>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
-          <t>脫單</t>
+          <t>冇晒菲士</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>脱单，找到对象</t>
+          <t>没面子</t>
         </is>
       </c>
       <c r="G539" t="inlineStr"/>
@@ -19303,18 +19311,18 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>摆pose</t>
+          <t>出pool</t>
         </is>
       </c>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>摆pose</t>
+          <t>脫單</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>摆姿势</t>
+          <t>脱单，找到对象</t>
         </is>
       </c>
       <c r="G540" t="inlineStr"/>
@@ -19333,25 +19341,21 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>蛋tart</t>
+          <t>摆pose</t>
         </is>
       </c>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>蛋挞</t>
+          <t>摆pose</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>蛋挞</t>
-        </is>
-      </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>egg tart</t>
-        </is>
-      </c>
+          <t>摆姿势</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr">
         <is>
           <t>False</t>
@@ -19367,23 +19371,23 @@
       <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
-          <t>車呔</t>
+          <t>蛋tart</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
-          <t>車呔</t>
+          <t>蛋挞</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>轮胎</t>
+          <t>蛋挞</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>tyre</t>
+          <t>egg tart</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -19398,26 +19402,26 @@
           <t>token</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>campus</t>
-        </is>
-      </c>
+      <c r="B543" t="inlineStr"/>
       <c r="C543" t="inlineStr">
         <is>
-          <t>tut</t>
+          <t>車呔</t>
         </is>
       </c>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
-          <t>tutorial</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr"/>
+          <t>車呔</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>轮胎</t>
+        </is>
+      </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>tutorial (small-group class)</t>
+          <t>tyre</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -19439,19 +19443,19 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>adp</t>
+          <t>tut</t>
         </is>
       </c>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
-          <t>加/退選期</t>
+          <t>tutorial</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
-          <t>add-drop period</t>
+          <t>tutorial (small-group class)</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -19473,19 +19477,19 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>reg</t>
+          <t>adp</t>
         </is>
       </c>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
-          <t>註冊/報名</t>
+          <t>加/退選期</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
-          <t>register / registration</t>
+          <t>add-drop period</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -19507,19 +19511,19 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>asm</t>
+          <t>reg</t>
         </is>
       </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>功課</t>
+          <t>註冊/報名</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
-          <t>assignment</t>
+          <t>register / registration</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -19541,19 +19545,19 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>prof</t>
+          <t>asm</t>
         </is>
       </c>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>功課</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>assignment</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -19575,19 +19579,19 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>rn</t>
+          <t>prof</t>
         </is>
       </c>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>而家</t>
+          <t>教授</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
-          <t>right now</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -19609,19 +19613,19 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>rn</t>
         </is>
       </c>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>今晚</t>
+          <t>而家</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
-          <t>tonight</t>
+          <t>right now</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -19643,23 +19647,19 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>leng grade</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>靚grade</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>容易拿A的课</t>
-        </is>
-      </c>
+          <t>今晚</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
-          <t>good grade course</t>
+          <t>tonight</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -19681,62 +19681,62 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>leng grade</t>
         </is>
       </c>
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Common Core</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr"/>
+          <t>靚grade</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>容易拿A的课</t>
+        </is>
+      </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Common Core (university course category)</t>
+          <t>good grade course</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>MTR station</t>
+          <t>campus</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>kennedy town</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>堅尼地城</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>堅尼地城</t>
-        </is>
-      </c>
+          <t>Common Core</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Kennedy Town MTR station</t>
+          <t>Common Core (university course category)</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -19753,23 +19753,23 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>sai ying pun</t>
+          <t>kennedy town</t>
         </is>
       </c>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>西營盤</t>
+          <t>堅尼地城</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>西營盤</t>
+          <t>堅尼地城</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Sai Ying Pun MTR station</t>
+          <t>Kennedy Town MTR station</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -19791,23 +19791,23 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>sheung wan</t>
+          <t>sai ying pun</t>
         </is>
       </c>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>上環</t>
+          <t>西營盤</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>上環</t>
+          <t>西營盤</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Sheung Wan MTR station</t>
+          <t>Sai Ying Pun MTR station</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -19819,7 +19819,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -19829,23 +19829,23 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>central</t>
+          <t>sheung wan</t>
         </is>
       </c>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>上環</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>上環</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Central MTR station</t>
+          <t>Sheung Wan MTR station</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -19867,23 +19867,23 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>central</t>
         </is>
       </c>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr">
         <is>
-          <t>金鐘</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>金鐘</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Admiralty MTR station</t>
+          <t>Central MTR station</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -19895,7 +19895,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -19905,23 +19905,23 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>wan chai</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr">
         <is>
-          <t>灣仔</t>
+          <t>金鐘</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>灣仔</t>
+          <t>金鐘</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Wan Chai MTR station</t>
+          <t>Admiralty MTR station</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -19943,23 +19943,23 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>causeway bay</t>
+          <t>wan chai</t>
         </is>
       </c>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
-          <t>銅鑼灣</t>
+          <t>灣仔</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>銅鑼灣</t>
+          <t>灣仔</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Causeway Bay MTR station</t>
+          <t>Wan Chai MTR station</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -19981,23 +19981,23 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>tin hau</t>
+          <t>causeway bay</t>
         </is>
       </c>
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr">
         <is>
-          <t>天后</t>
+          <t>銅鑼灣</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>天后</t>
+          <t>銅鑼灣</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Tin Hau MTR station</t>
+          <t>Causeway Bay MTR station</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -20019,23 +20019,23 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>fortress hill</t>
+          <t>tin hau</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
-          <t>炮台山</t>
+          <t>天后</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>炮台山</t>
+          <t>天后</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Fortress Hill MTR station</t>
+          <t>Tin Hau MTR station</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -20057,23 +20057,23 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>north point</t>
+          <t>fortress hill</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
-          <t>北角</t>
+          <t>炮台山</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>北角</t>
+          <t>炮台山</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>North Point MTR station</t>
+          <t>Fortress Hill MTR station</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -20095,23 +20095,23 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>quarry bay</t>
+          <t>north point</t>
         </is>
       </c>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
-          <t>鰂魚涌</t>
+          <t>北角</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>鰂魚涌</t>
+          <t>北角</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Quarry Bay MTR station</t>
+          <t>North Point MTR station</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -20133,23 +20133,23 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>tai koo</t>
+          <t>quarry bay</t>
         </is>
       </c>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
         <is>
-          <t>太古</t>
+          <t>鰂魚涌</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>太古</t>
+          <t>鰂魚涌</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Tai Koo MTR station</t>
+          <t>Quarry Bay MTR station</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -20171,23 +20171,23 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>sai wan ho</t>
+          <t>tai koo</t>
         </is>
       </c>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
-          <t>西灣河</t>
+          <t>太古</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>西灣河</t>
+          <t>太古</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Sai Wan Ho MTR station</t>
+          <t>Tai Koo MTR station</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -20209,23 +20209,23 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>shau kei wan</t>
+          <t>sai wan ho</t>
         </is>
       </c>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
-          <t>筲箕灣</t>
+          <t>西灣河</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>筲箕灣</t>
+          <t>西灣河</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Shau Kei Wan MTR station</t>
+          <t>Sai Wan Ho MTR station</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -20247,23 +20247,23 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>heng fa chuen</t>
+          <t>shau kei wan</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>杏花邨</t>
+          <t>筲箕灣</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>杏花邨</t>
+          <t>筲箕灣</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>Heng Fa Chuen MTR station</t>
+          <t>Shau Kei Wan MTR station</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -20285,23 +20285,23 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>chai wan</t>
+          <t>heng fa chuen</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>柴灣</t>
+          <t>杏花邨</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>柴灣</t>
+          <t>杏花邨</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Chai Wan MTR station</t>
+          <t>Heng Fa Chuen MTR station</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -20313,7 +20313,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -20323,23 +20323,23 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>jordan</t>
+          <t>chai wan</t>
         </is>
       </c>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
-          <t>佐敦</t>
+          <t>柴灣</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>佐敦</t>
+          <t>柴灣</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Jordan MTR station</t>
+          <t>Chai Wan MTR station</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -20351,7 +20351,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -20361,23 +20361,23 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>yau ma tei</t>
+          <t>jordan</t>
         </is>
       </c>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr">
         <is>
-          <t>油麻地</t>
+          <t>佐敦</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>油麻地</t>
+          <t>佐敦</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>Yau Ma Tei MTR station</t>
+          <t>Jordan MTR station</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -20399,23 +20399,23 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>prince edward</t>
+          <t>yau ma tei</t>
         </is>
       </c>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
-          <t>太子</t>
+          <t>油麻地</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>太子</t>
+          <t>油麻地</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Prince Edward MTR station</t>
+          <t>Yau Ma Tei MTR station</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -20437,23 +20437,23 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>sham shui po</t>
+          <t>prince edward</t>
         </is>
       </c>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
-          <t>深水埗</t>
+          <t>太子</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>深水埗</t>
+          <t>太子</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Sham Shui Po MTR station</t>
+          <t>Prince Edward MTR station</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -20475,23 +20475,23 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>cheung sha wan</t>
+          <t>sham shui po</t>
         </is>
       </c>
       <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
-          <t>長沙灣</t>
+          <t>深水埗</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>長沙灣</t>
+          <t>深水埗</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Cheung Sha Wan MTR station</t>
+          <t>Sham Shui Po MTR station</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -20513,23 +20513,23 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>lai chi kok</t>
+          <t>cheung sha wan</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>荔枝角</t>
+          <t>長沙灣</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>荔枝角</t>
+          <t>長沙灣</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Lai Chi Kok MTR station</t>
+          <t>Cheung Sha Wan MTR station</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -20551,23 +20551,23 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>mei foo</t>
+          <t>lai chi kok</t>
         </is>
       </c>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>美孚</t>
+          <t>荔枝角</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>美孚</t>
+          <t>荔枝角</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>Mei Foo MTR station</t>
+          <t>Lai Chi Kok MTR station</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -20589,23 +20589,23 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>lai king</t>
+          <t>mei foo</t>
         </is>
       </c>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
-          <t>荔景</t>
+          <t>美孚</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>荔景</t>
+          <t>美孚</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Lai King MTR station</t>
+          <t>Mei Foo MTR station</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -20627,23 +20627,23 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>kwai fong</t>
+          <t>lai king</t>
         </is>
       </c>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>葵芳</t>
+          <t>荔景</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>葵芳</t>
+          <t>荔景</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>Kwai Fong MTR station</t>
+          <t>Lai King MTR station</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -20665,23 +20665,23 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>kwai hing</t>
+          <t>kwai fong</t>
         </is>
       </c>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>葵興</t>
+          <t>葵芳</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>葵興</t>
+          <t>葵芳</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Kwai Hing MTR station</t>
+          <t>Kwai Fong MTR station</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -20703,23 +20703,23 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>tai wo hau</t>
+          <t>kwai hing</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>大窩口</t>
+          <t>葵興</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>大窩口</t>
+          <t>葵興</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Tai Wo Hau MTR station</t>
+          <t>Kwai Hing MTR station</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -20741,23 +20741,23 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>tsuen wan</t>
+          <t>tai wo hau</t>
         </is>
       </c>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>荃灣</t>
+          <t>大窩口</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>荃灣</t>
+          <t>大窩口</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Tsuen Wan MTR station</t>
+          <t>Tai Wo Hau MTR station</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -20769,7 +20769,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -20779,23 +20779,23 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>whampoa</t>
+          <t>tsuen wan</t>
         </is>
       </c>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>黃埔</t>
+          <t>荃灣</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>黃埔</t>
+          <t>荃灣</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Whampoa MTR station</t>
+          <t>Tsuen Wan MTR station</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -20807,7 +20807,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -20817,23 +20817,23 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>ho man tin</t>
+          <t>whampoa</t>
         </is>
       </c>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>何文田</t>
+          <t>黃埔</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>何文田</t>
+          <t>黃埔</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Ho Man Tin MTR station</t>
+          <t>Whampoa MTR station</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -20855,23 +20855,23 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>shek kip mei</t>
+          <t>ho man tin</t>
         </is>
       </c>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>石硤尾</t>
+          <t>何文田</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>石硤尾</t>
+          <t>何文田</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Shek Kip Mei MTR station</t>
+          <t>Ho Man Tin MTR station</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -20893,23 +20893,23 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>kowloon tong</t>
+          <t>shek kip mei</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>九龍塘</t>
+          <t>石硤尾</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>九龍塘</t>
+          <t>石硤尾</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Kowloon Tong MTR station</t>
+          <t>Shek Kip Mei MTR station</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -20931,23 +20931,23 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>lok fu</t>
+          <t>kowloon tong</t>
         </is>
       </c>
       <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
-          <t>樂富</t>
+          <t>九龍塘</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>樂富</t>
+          <t>九龍塘</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Lok Fu MTR station</t>
+          <t>Kowloon Tong MTR station</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -20969,23 +20969,23 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>wong tai sin</t>
+          <t>lok fu</t>
         </is>
       </c>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
-          <t>黃大仙</t>
+          <t>樂富</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>黃大仙</t>
+          <t>樂富</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Wong Tai Sin MTR station</t>
+          <t>Lok Fu MTR station</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -21007,23 +21007,23 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>diamond hill</t>
+          <t>wong tai sin</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>鑽石山</t>
+          <t>黃大仙</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>鑽石山</t>
+          <t>黃大仙</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Diamond Hill MTR station</t>
+          <t>Wong Tai Sin MTR station</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -21045,23 +21045,23 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>choi hung</t>
+          <t>diamond hill</t>
         </is>
       </c>
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>彩虹</t>
+          <t>鑽石山</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>彩虹</t>
+          <t>鑽石山</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Choi Hung MTR station</t>
+          <t>Diamond Hill MTR station</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -21083,23 +21083,23 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>kowloon bay</t>
+          <t>choi hung</t>
         </is>
       </c>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>九龍灣</t>
+          <t>彩虹</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>九龍灣</t>
+          <t>彩虹</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Kowloon Bay MTR station</t>
+          <t>Choi Hung MTR station</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -21121,23 +21121,23 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>ngau tau kok</t>
+          <t>kowloon bay</t>
         </is>
       </c>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>牛頭角</t>
+          <t>九龍灣</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>牛頭角</t>
+          <t>九龍灣</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Ngau Tau Kok MTR station</t>
+          <t>Kowloon Bay MTR station</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -21159,23 +21159,23 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>kwun tong</t>
+          <t>ngau tau kok</t>
         </is>
       </c>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>觀塘</t>
+          <t>牛頭角</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>觀塘</t>
+          <t>牛頭角</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Kwun Tong MTR station</t>
+          <t>Ngau Tau Kok MTR station</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -21197,23 +21197,23 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>lam tin</t>
+          <t>kwun tong</t>
         </is>
       </c>
       <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
-          <t>藍田</t>
+          <t>觀塘</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>藍田</t>
+          <t>觀塘</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Lam Tin MTR station</t>
+          <t>Kwun Tong MTR station</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -21235,23 +21235,23 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>yau tong</t>
+          <t>lam tin</t>
         </is>
       </c>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>油塘</t>
+          <t>藍田</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>油塘</t>
+          <t>藍田</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Yau Tong MTR station</t>
+          <t>Lam Tin MTR station</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -21273,23 +21273,23 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>tiu keng leng</t>
+          <t>yau tong</t>
         </is>
       </c>
       <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
-          <t>調景嶺</t>
+          <t>油塘</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>調景嶺</t>
+          <t>油塘</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Tiu Keng Leng MTR station</t>
+          <t>Yau Tong MTR station</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -21311,23 +21311,23 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>hang hau</t>
+          <t>tiu keng leng</t>
         </is>
       </c>
       <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>坑口</t>
+          <t>調景嶺</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>坑口</t>
+          <t>調景嶺</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Hang Hau MTR station</t>
+          <t>Tiu Keng Leng MTR station</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -21349,23 +21349,23 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>po lam</t>
+          <t>hang hau</t>
         </is>
       </c>
       <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
-          <t>寶琳</t>
+          <t>坑口</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>寶琳</t>
+          <t>坑口</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Po Lam MTR station</t>
+          <t>Hang Hau MTR station</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -21387,23 +21387,23 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>hong kong</t>
+          <t>po lam</t>
         </is>
       </c>
       <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>寶琳</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>寶琳</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Hong Kong MTR station</t>
+          <t>Po Lam MTR station</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -21415,7 +21415,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -21425,23 +21425,23 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>kowloon</t>
+          <t>hong kong</t>
         </is>
       </c>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
-          <t>九龍</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>九龍</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Kowloon MTR station</t>
+          <t>Hong Kong MTR station</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -21463,23 +21463,23 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>olympic</t>
+          <t>kowloon</t>
         </is>
       </c>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
-          <t>奧運</t>
+          <t>九龍</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>奧運</t>
+          <t>九龍</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Olympic MTR station</t>
+          <t>Kowloon MTR station</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -21491,7 +21491,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -21501,23 +21501,23 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>nam cheong</t>
+          <t>olympic</t>
         </is>
       </c>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
-          <t>南昌</t>
+          <t>奧運</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>南昌</t>
+          <t>奧運</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Nam Cheong MTR station</t>
+          <t>Olympic MTR station</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -21539,23 +21539,23 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>tsing yi</t>
+          <t>nam cheong</t>
         </is>
       </c>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
-          <t>青衣</t>
+          <t>南昌</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>青衣</t>
+          <t>南昌</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Tsing Yi MTR station</t>
+          <t>Nam Cheong MTR station</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -21577,23 +21577,23 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>sunny bay</t>
+          <t>tsing yi</t>
         </is>
       </c>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
-          <t>欣澳</t>
+          <t>青衣</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>欣澳</t>
+          <t>青衣</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Sunny Bay MTR station</t>
+          <t>Tsing Yi MTR station</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -21615,23 +21615,23 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>tung chung</t>
+          <t>sunny bay</t>
         </is>
       </c>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>東涌</t>
+          <t>欣澳</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>東涌</t>
+          <t>欣澳</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Tung Chung MTR station</t>
+          <t>Sunny Bay MTR station</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -21653,23 +21653,23 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>disneyland resort</t>
+          <t>tung chung</t>
         </is>
       </c>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr">
         <is>
-          <t>迪士尼</t>
+          <t>東涌</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>迪士尼</t>
+          <t>東涌</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Disneyland Resort MTR station</t>
+          <t>Tung Chung MTR station</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -21681,7 +21681,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -21691,23 +21691,23 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>airport</t>
+          <t>disneyland resort</t>
         </is>
       </c>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>機場</t>
+          <t>迪士尼</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>機場</t>
+          <t>迪士尼</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Airport MTR station</t>
+          <t>Disneyland Resort MTR station</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -21729,23 +21729,23 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>asiaworld-expo</t>
+          <t>airport</t>
         </is>
       </c>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr">
         <is>
-          <t>博覽館</t>
+          <t>機場</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>博覽館</t>
+          <t>機場</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Asiaworld-Expo MTR station</t>
+          <t>Airport MTR station</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -21757,7 +21757,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -21767,23 +21767,23 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>exhibition centre</t>
+          <t>asiaworld-expo</t>
         </is>
       </c>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr">
         <is>
-          <t>會展</t>
+          <t>博覽館</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>會展</t>
+          <t>博覽館</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Exhibition Centre MTR station</t>
+          <t>Asiaworld-Expo MTR station</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -21805,23 +21805,23 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>hung hom</t>
+          <t>exhibition centre</t>
         </is>
       </c>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr">
         <is>
-          <t>紅磡</t>
+          <t>會展</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>紅磡</t>
+          <t>會展</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Hung Hom MTR station</t>
+          <t>Exhibition Centre MTR station</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -21843,23 +21843,23 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>mong kok east</t>
+          <t>hung hom</t>
         </is>
       </c>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr">
         <is>
-          <t>旺角東</t>
+          <t>紅磡</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>旺角東</t>
+          <t>紅磡</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Mong Kok East MTR station</t>
+          <t>Hung Hom MTR station</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -21881,23 +21881,23 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>tai wai</t>
+          <t>mong kok east</t>
         </is>
       </c>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr">
         <is>
-          <t>大圍</t>
+          <t>旺角東</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>大圍</t>
+          <t>旺角東</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Tai Wai MTR station</t>
+          <t>Mong Kok East MTR station</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -21919,23 +21919,23 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>sha tin</t>
+          <t>tai wai</t>
         </is>
       </c>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr">
         <is>
-          <t>沙田</t>
+          <t>大圍</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>沙田</t>
+          <t>大圍</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Sha Tin MTR station</t>
+          <t>Tai Wai MTR station</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -21957,23 +21957,23 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>fo tan</t>
+          <t>sha tin</t>
         </is>
       </c>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
         <is>
-          <t>火炭</t>
+          <t>沙田</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>火炭</t>
+          <t>沙田</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Fo Tan MTR station</t>
+          <t>Sha Tin MTR station</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -21985,7 +21985,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -21995,23 +21995,23 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>racecourse</t>
+          <t>fo tan</t>
         </is>
       </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr">
         <is>
-          <t>馬場</t>
+          <t>火炭</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>馬場</t>
+          <t>火炭</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Racecourse MTR station</t>
+          <t>Fo Tan MTR station</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -22033,23 +22033,23 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>racecourse</t>
         </is>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
-          <t>大學</t>
+          <t>馬場</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>大學</t>
+          <t>馬場</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>University MTR station</t>
+          <t>Racecourse MTR station</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -22061,7 +22061,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -22071,23 +22071,23 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>tai po market</t>
+          <t>university</t>
         </is>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
-          <t>大埔墟</t>
+          <t>大學</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>大埔墟</t>
+          <t>大學</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Tai Po Market MTR station</t>
+          <t>University MTR station</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -22109,23 +22109,23 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>tai wo</t>
+          <t>tai po market</t>
         </is>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
         <is>
-          <t>太和</t>
+          <t>大埔墟</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>太和</t>
+          <t>大埔墟</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>Tai Wo MTR station</t>
+          <t>Tai Po Market MTR station</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -22137,7 +22137,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -22147,23 +22147,23 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>fanling</t>
+          <t>tai wo</t>
         </is>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
-          <t>粉嶺</t>
+          <t>太和</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>粉嶺</t>
+          <t>太和</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>Fanling MTR station</t>
+          <t>Tai Wo MTR station</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -22175,7 +22175,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -22185,23 +22185,23 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>sheung shui</t>
+          <t>fanling</t>
         </is>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
-          <t>上水</t>
+          <t>粉嶺</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>上水</t>
+          <t>粉嶺</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>Sheung Shui MTR station</t>
+          <t>Fanling MTR station</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -22223,23 +22223,23 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>lo wu</t>
+          <t>sheung shui</t>
         </is>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
-          <t>羅湖</t>
+          <t>上水</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>羅湖</t>
+          <t>上水</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Lo Wu MTR station</t>
+          <t>Sheung Shui MTR station</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -22261,23 +22261,23 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>lok ma chau</t>
+          <t>lo wu</t>
         </is>
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
-          <t>落馬洲</t>
+          <t>羅湖</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>落馬洲</t>
+          <t>羅湖</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>Lok Ma Chau MTR station</t>
+          <t>Lo Wu MTR station</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -22289,7 +22289,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -22299,23 +22299,23 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>tko</t>
+          <t>lok ma chau</t>
         </is>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>將軍澳</t>
+          <t>落馬洲</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>將軍澳</t>
+          <t>落馬洲</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Tseung Kwan O MTR station</t>
+          <t>Lok Ma Chau MTR station</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -22337,23 +22337,23 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>tst</t>
+          <t>tko</t>
         </is>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr">
         <is>
-          <t>尖沙咀</t>
+          <t>將軍澳</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>尖沙咀</t>
+          <t>將軍澳</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Tsim Sha Tsui MTR station</t>
+          <t>Tseung Kwan O MTR station</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -22375,23 +22375,23 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>lohas</t>
+          <t>tst</t>
         </is>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
         <is>
-          <t>康城</t>
+          <t>尖沙咀</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>康城</t>
+          <t>尖沙咀</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>LOHAS Park MTR station</t>
+          <t>Tsim Sha Tsui MTR station</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -22413,23 +22413,23 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>hku</t>
+          <t>lohas</t>
         </is>
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr">
         <is>
-          <t>香港大學</t>
+          <t>康城</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>香港大學</t>
+          <t>康城</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>HKU (station &amp; university)</t>
+          <t>LOHAS Park MTR station</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -22446,32 +22446,28 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>MTR station</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>poly</t>
-        </is>
-      </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>polyu</t>
-        </is>
-      </c>
+          <t>hku</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
-          <t>香港理工大學</t>
+          <t>香港大學</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>香港理工大學</t>
+          <t>香港大學</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>PolyU (Hong Kong Polytechnic University)</t>
+          <t>HKU (station &amp; university)</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -22493,23 +22489,27 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>ust</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr"/>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>polyu</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>香港科技大學</t>
+          <t>香港理工大學</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>香港科技大學</t>
+          <t>香港理工大學</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>HKUST (Hong Kong University of Science and Technology)</t>
+          <t>PolyU (Hong Kong Polytechnic University)</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -22526,71 +22526,71 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MTR station</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>mk</t>
+          <t>ust</t>
         </is>
       </c>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr">
         <is>
-          <t>旺角</t>
+          <t>香港科技大學</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>旺角</t>
+          <t>香港科技大學</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Mong Kok MTR station</t>
+          <t>HKUST (Hong Kong University of Science and Technology)</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>campus</t>
+          <t>MTR station</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>ging guo</t>
+          <t>mk</t>
         </is>
       </c>
       <c r="D627" t="inlineStr"/>
       <c r="E627" t="inlineStr">
         <is>
-          <t>勁過</t>
+          <t>旺角</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>考試/成績很好(GPA≥3.0，也用作打氣語)</t>
+          <t>旺角</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>doing great / GPA&gt;=3.0 (also used as an exam-time greeting)</t>
+          <t>Mong Kok MTR station</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -22607,23 +22607,23 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>tui guo</t>
+          <t>ging guo</t>
         </is>
       </c>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr">
         <is>
-          <t>頹過</t>
+          <t>勁過</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>勉強及格(GPA 2-2.9)</t>
+          <t>考試/成績很好(GPA≥3.0，也用作打氣語)</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>passed with a mediocre GPA (2.0-2.9)</t>
+          <t>doing great / GPA&gt;=3.0 (also used as an exam-time greeting)</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -22645,23 +22645,23 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>m guo</t>
+          <t>tui guo</t>
         </is>
       </c>
       <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr">
         <is>
-          <t>唔過</t>
+          <t>頹過</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>不及格(GPA過低未能過關)</t>
+          <t>勉強及格(GPA 2-2.9)</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>failed to pass (GPA below the passing threshold)</t>
+          <t>passed with a mediocre GPA (2.0-2.9)</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -22683,23 +22683,23 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>guo saam</t>
+          <t>m guo</t>
         </is>
       </c>
       <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
-          <t>過三</t>
+          <t>唔過</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>GPA高於3</t>
+          <t>不及格(GPA過低未能過關)</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>GPA above 3.0</t>
+          <t>failed to pass (GPA below the passing threshold)</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -22721,23 +22721,23 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>baau sei</t>
+          <t>guo saam</t>
         </is>
       </c>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
-          <t>爆四</t>
+          <t>過三</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>GPA接近或等於4(近滿分)</t>
+          <t>GPA高於3</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>GPA near or at 4.0 (near-perfect)</t>
+          <t>GPA above 3.0</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -22759,23 +22759,23 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>tin dei tong</t>
+          <t>baau sei</t>
         </is>
       </c>
       <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr">
         <is>
-          <t>天地堂</t>
+          <t>爆四</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>一日之內課堂間隔極長</t>
+          <t>GPA接近或等於4(近滿分)</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>class schedule with a huge gap between classes on the same day</t>
+          <t>GPA near or at 4.0 (near-perfect)</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -22787,7 +22787,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -22797,23 +22797,23 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>zong</t>
+          <t>tin dei tong</t>
         </is>
       </c>
       <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>莊</t>
+          <t>天地堂</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>大學學會/學生會的內閣</t>
+          <t>一日之內課堂間隔極長</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>student society/union's committee ("cabinet")</t>
+          <t>class schedule with a huge gap between classes on the same day</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -22825,7 +22825,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -22835,23 +22835,23 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>soeng zong</t>
+          <t>zong</t>
         </is>
       </c>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>上莊</t>
+          <t>莊</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>擔任學會/學生會幹事</t>
+          <t>大學學會/學生會的內閣</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>serve as an officer in a student society/union</t>
+          <t>student society/union's committee ("cabinet")</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -22873,23 +22873,23 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>zong jau</t>
+          <t>soeng zong</t>
         </is>
       </c>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>莊友</t>
+          <t>上莊</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>同屆學會幹事</t>
+          <t>擔任學會/學生會幹事</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>fellow officers of the same committee</t>
+          <t>serve as an officer in a student society/union</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -22911,23 +22911,23 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>ziu zong</t>
+          <t>zong jau</t>
         </is>
       </c>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
-          <t>招莊</t>
+          <t>莊友</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>招募下一屆幹事</t>
+          <t>同屆學會幹事</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>recruiting the next committee</t>
+          <t>fellow officers of the same committee</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -22949,23 +22949,23 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>king zong</t>
+          <t>ziu zong</t>
         </is>
       </c>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr">
         <is>
-          <t>傾莊</t>
+          <t>招莊</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>商討來年學會計劃</t>
+          <t>招募下一屆幹事</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>discuss next year's plans for the committee</t>
+          <t>recruiting the next committee</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -22987,23 +22987,23 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>zyun zong</t>
+          <t>king zong</t>
         </is>
       </c>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
-          <t>轉莊</t>
+          <t>傾莊</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>新舊幹事交接</t>
+          <t>商討來年學會計劃</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>handover between old and new committee</t>
+          <t>discuss next year's plans for the committee</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -23025,23 +23025,23 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>lok zong</t>
+          <t>zyun zong</t>
         </is>
       </c>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
-          <t>落莊</t>
+          <t>轉莊</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>幹事任期結束卸任</t>
+          <t>新舊幹事交接</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>stepping down after a committee term</t>
+          <t>handover between old and new committee</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -23053,7 +23053,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -23063,23 +23063,23 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>lok zong</t>
         </is>
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
-          <t>蛇</t>
+          <t>落莊</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>非宿生偷偷留宿</t>
+          <t>幹事任期結束卸任</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>a non-resident secretly staying overnight in a dorm</t>
+          <t>stepping down after a committee term</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -23091,7 +23091,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -23101,23 +23101,23 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>wat se</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
-          <t>屈蛇</t>
+          <t>蛇</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>非宿生偷偷留宿(動詞)</t>
+          <t>非宿生偷偷留宿</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>to secretly stay overnight in a dorm as a non-resident</t>
+          <t>a non-resident secretly staying overnight in a dorm</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -23139,23 +23139,23 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>jyun jyun se</t>
+          <t>wat se</t>
         </is>
       </c>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
-          <t>鴛鴦蛇</t>
+          <t>屈蛇</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>偷偷留宿異性宿舍</t>
+          <t>非宿生偷偷留宿(動詞)</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>secretly staying overnight in an opposite-gender dorm</t>
+          <t>to secretly stay overnight in a dorm as a non-resident</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -23177,23 +23177,23 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>daa se</t>
+          <t>jyun jyun se</t>
         </is>
       </c>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>打蛇</t>
+          <t>鴛鴦蛇</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>校方巡查非法留宿</t>
+          <t>偷偷留宿異性宿舍</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>dorm staff checking for illegal overnight stayers</t>
+          <t>secretly staying overnight in an opposite-gender dorm</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -23215,23 +23215,23 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>teoi jau</t>
+          <t>daa se</t>
         </is>
       </c>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
-          <t>頹友</t>
+          <t>打蛇</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>無心向學、只求合格的人</t>
+          <t>校方巡查非法留宿</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>someone who doesn't study seriously, just aims to pass</t>
+          <t>dorm staff checking for illegal overnight stayers</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -23253,23 +23253,23 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>zip jau</t>
+          <t>teoi jau</t>
         </is>
       </c>
       <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>摺友</t>
+          <t>頹友</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>不參加社交、只顧自己的人</t>
+          <t>無心向學、只求合格的人</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>someone who avoids socializing and stays in their own world</t>
+          <t>someone who doesn't study seriously, just aims to pass</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -23291,23 +23291,23 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>zip laa baa</t>
+          <t>zip jau</t>
         </is>
       </c>
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
-          <t>摺拉把</t>
+          <t>摺友</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>經常躲圖書館溫書、不參加活動的人</t>
+          <t>不參加社交、只顧自己的人</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>someone always in the library studying, never joining activities</t>
+          <t>someone who avoids socializing and stays in their own world</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -23329,23 +23329,23 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>saat jan wong</t>
+          <t>zip laa baa</t>
         </is>
       </c>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
-          <t>殺人王</t>
+          <t>摺拉把</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>評分極嚴苛的老師</t>
+          <t>經常躲圖書館溫書、不參加活動的人</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>a professor who grades extremely harshly</t>
+          <t>someone always in the library studying, never joining activities</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -23367,23 +23367,23 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>saat sau</t>
+          <t>saat jan wong</t>
         </is>
       </c>
       <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>殺手</t>
+          <t>殺人王</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>評分極嚴苛的老師(同殺人王)</t>
+          <t>評分極嚴苛的老師</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>a professor who grades extremely harshly (same as 殺人王)</t>
+          <t>a professor who grades extremely harshly</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -23395,7 +23395,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -23405,23 +23405,23 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>nds</t>
+          <t>saat sau</t>
         </is>
       </c>
       <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>NDS</t>
+          <t>殺手</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>內地生(取普通話拼音Nei Di Sheng)</t>
+          <t>評分極嚴苛的老師(同殺人王)</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>mainland Chinese student</t>
+          <t>a professor who grades extremely harshly (same as 殺人王)</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -23443,23 +23443,23 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>psp</t>
+          <t>nds</t>
         </is>
       </c>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr">
         <is>
-          <t>PSP</t>
+          <t>NDS</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>內地生(Putonghua Speaking People)</t>
+          <t>內地生(取普通話拼音Nei Di Sheng)</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>mainland Chinese student (Putonghua Speaking People)</t>
+          <t>mainland Chinese student</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -23471,7 +23471,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -23481,23 +23481,23 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>chiu sin</t>
+          <t>psp</t>
         </is>
       </c>
       <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr">
         <is>
-          <t>超仙</t>
+          <t>PSP</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>大四學長</t>
+          <t>內地生(Putonghua Speaking People)</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>4th-year senior student</t>
+          <t>mainland Chinese student (Putonghua Speaking People)</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -23519,23 +23519,23 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>daai sin</t>
+          <t>chiu sin</t>
         </is>
       </c>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr">
         <is>
-          <t>大仙</t>
+          <t>超仙</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>大三學長</t>
+          <t>大四學長</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>3rd-year senior student</t>
+          <t>4th-year senior student</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -23557,23 +23557,23 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>sai sin</t>
+          <t>daai sin</t>
         </is>
       </c>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
-          <t>細仙</t>
+          <t>大仙</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>大二學長</t>
+          <t>大三學長</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>2nd-year senior student</t>
+          <t>3rd-year senior student</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -23595,23 +23595,23 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>lou gwai</t>
+          <t>sai sin</t>
         </is>
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr">
         <is>
-          <t>老鬼</t>
+          <t>細仙</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>已畢業的學生(尤指前任幹事)</t>
+          <t>大二學長</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>a graduated alum, especially a former committee officer</t>
+          <t>2nd-year senior student</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -23633,23 +23633,23 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>free rider</t>
+          <t>lou gwai</t>
         </is>
       </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Free Rider</t>
+          <t>老鬼</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>小組作業中不負責任的組員</t>
+          <t>已畢業的學生(尤指前任幹事)</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>a group project member who doesn't contribute</t>
+          <t>a graduated alum, especially a former committee officer</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -23671,23 +23671,23 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>sem</t>
+          <t>free rider</t>
         </is>
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Sem</t>
+          <t>Free Rider</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>學期(Semester)</t>
+          <t>小組作業中不負責任的組員</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>semester</t>
+          <t>a group project member who doesn't contribute</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -23699,7 +23699,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -23709,23 +23709,23 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>teoi faan</t>
+          <t>sem</t>
         </is>
       </c>
       <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
-          <t>頹飯</t>
+          <t>Sem</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>大學飯堂低價但質素差的飯餐</t>
+          <t>學期(Semester)</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>cheap, low-quality canteen meal</t>
+          <t>semester</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -23747,23 +23747,23 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>saat pei</t>
+          <t>teoi faan</t>
         </is>
       </c>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr">
         <is>
-          <t>撻皮</t>
+          <t>頹飯</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>做事散漫不積極</t>
+          <t>大學飯堂低價但質素差的飯餐</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>careless, lazy attitude towards responsibilities</t>
+          <t>cheap, low-quality canteen meal</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -23785,23 +23785,23 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>bj zai</t>
+          <t>saat pei</t>
         </is>
       </c>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr">
         <is>
-          <t>BJ仔</t>
+          <t>撻皮</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>博盡仔，拼盡全力做事的人</t>
+          <t>做事散漫不積極</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>someone who gives their all-out effort ("博盡仔")</t>
+          <t>careless, lazy attitude towards responsibilities</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -23813,7 +23813,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -23823,23 +23823,23 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>bjmf</t>
+          <t>bj zai</t>
         </is>
       </c>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr">
         <is>
-          <t>BJMF</t>
+          <t>BJ仔</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>搏盡無悔，全力以赴無悔</t>
+          <t>博盡仔，拼盡全力做事的人</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>"all-out effort, no regrets" ("搏盡無悔")</t>
+          <t>someone who gives their all-out effort ("博盡仔")</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -23861,23 +23861,23 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>su</t>
+          <t>bjmf</t>
         </is>
       </c>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>BJMF</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>學生會(Student Union)</t>
+          <t>搏盡無悔，全力以赴無悔</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Student Union</t>
+          <t>"all-out effort, no regrets" ("搏盡無悔")</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -23899,23 +23899,23 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>hall</t>
+          <t>su</t>
         </is>
       </c>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>大學宿舍</t>
+          <t>學生會(Student Union)</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>university dormitory</t>
+          <t>Student Union</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -23927,7 +23927,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>token</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -23937,23 +23937,23 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>laai baa</t>
+          <t>hall</t>
         </is>
       </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
-          <t>拉把</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>圖書館(取library的libra發音)</t>
+          <t>大學宿舍</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>library (from the "libra" part of "library")</t>
+          <t>university dormitory</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -23975,23 +23975,23 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>gau can</t>
+          <t>laai baa</t>
         </is>
       </c>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>舊Can</t>
+          <t>拉把</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>舊飯堂(相對新飯堂而言)</t>
+          <t>圖書館(取library的libra發音)</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>the older canteen (as opposed to a newer one)</t>
+          <t>library (from the "libra" part of "library")</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -24013,23 +24013,23 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>san can</t>
+          <t>gau can</t>
         </is>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr">
         <is>
-          <t>新Can</t>
+          <t>舊Can</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>新落成的飯堂</t>
+          <t>舊飯堂(相對新飯堂而言)</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>a newly built canteen</t>
+          <t>the older canteen (as opposed to a newer one)</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -24051,23 +24051,23 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>fresh grad</t>
+          <t>san can</t>
         </is>
       </c>
       <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Fresh Grad</t>
+          <t>新Can</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>剛畢業的大學生</t>
+          <t>新落成的飯堂</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>a recently graduated university student</t>
+          <t>a newly built canteen</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -24079,7 +24079,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -24089,26 +24089,64 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>freshman</t>
+          <t>fresh grad</t>
         </is>
       </c>
       <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr">
         <is>
+          <t>Fresh Grad</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>剛畢業的大學生</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>a recently graduated university student</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>campus</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>freshman</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr">
+        <is>
           <t>Freshman</t>
         </is>
       </c>
-      <c r="F667" t="inlineStr">
+      <c r="F668" t="inlineStr">
         <is>
           <t>新入學的大一學生</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
+      <c r="G668" t="inlineStr">
         <is>
           <t>a first-year university student</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
+      <c r="H668" t="inlineStr">
         <is>
           <t>False</t>
         </is>
